--- a/01_Basic Model/02_Input Data/02_Future/DE_Future_Input_yearly.xlsx
+++ b/01_Basic Model/02_Input Data/02_Future/DE_Future_Input_yearly.xlsx
@@ -1,12 +1,205 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Competitiveness_of_RES\01_Basic Model\02_Input Data\02_Future\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DC39B7-F67D-45FF-AEE9-84D19A0926FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="38280" yWindow="45" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{9BA085BD-A4BD-4D3B-9BBD-ABB9433EC046}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="fuel_conv" sheetId="1" r:id="rId1"/>
+    <sheet name="fuel_renew" sheetId="2" r:id="rId2"/>
+    <sheet name="tech_conv" sheetId="3" r:id="rId3"/>
+    <sheet name="outages_conv" sheetId="8" r:id="rId4"/>
+    <sheet name="tech_renew" sheetId="4" r:id="rId5"/>
+    <sheet name="tech_stor" sheetId="5" r:id="rId6"/>
+    <sheet name="co2" sheetId="6" r:id="rId7"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="47">
+  <si>
+    <t>fuelprice</t>
+  </si>
+  <si>
+    <t>uranium</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>hardcoal</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>solar</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>bioenergy</t>
+  </si>
+  <si>
+    <t>waste</t>
+  </si>
+  <si>
+    <t>otherres</t>
+  </si>
+  <si>
+    <t>othergas</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>ccgt</t>
+  </si>
+  <si>
+    <t>ocgt</t>
+  </si>
+  <si>
+    <t>solar1</t>
+  </si>
+  <si>
+    <t>solar2</t>
+  </si>
+  <si>
+    <t>solar3</t>
+  </si>
+  <si>
+    <t>solar4</t>
+  </si>
+  <si>
+    <t>windonshore1</t>
+  </si>
+  <si>
+    <t>windonshore2</t>
+  </si>
+  <si>
+    <t>windonshore3</t>
+  </si>
+  <si>
+    <t>windonshore4</t>
+  </si>
+  <si>
+    <t>windoffshore</t>
+  </si>
+  <si>
+    <t>runofriver</t>
+  </si>
+  <si>
+    <t>reservoir</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>marine</t>
+  </si>
+  <si>
+    <t>pumpstorage</t>
+  </si>
+  <si>
+    <t>battery</t>
+  </si>
+  <si>
+    <t>carbonprice</t>
+  </si>
+  <si>
+    <t>efficiency</t>
+  </si>
+  <si>
+    <t>gmin</t>
+  </si>
+  <si>
+    <t>lifetime_eco</t>
+  </si>
+  <si>
+    <t>covernight</t>
+  </si>
+  <si>
+    <t>startup_fuelconsumption</t>
+  </si>
+  <si>
+    <t>startup_fixcost</t>
+  </si>
+  <si>
+    <t>avail</t>
+  </si>
+  <si>
+    <t>carboncontent</t>
+  </si>
+  <si>
+    <t>renew_disp</t>
+  </si>
+  <si>
+    <t>renew_curt</t>
+  </si>
+  <si>
+    <t>covernight_kW</t>
+  </si>
+  <si>
+    <t>covernight_MWh</t>
+  </si>
+  <si>
+    <t>storageduration</t>
+  </si>
+  <si>
+    <t>discharge_to_charge_ratio</t>
+  </si>
+  <si>
+    <t>cvarom MWh</t>
+  </si>
+  <si>
+    <t>*cfix</t>
+  </si>
+</sst>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="[$-1010809]dd/mm/yyyy"/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0.00\ &quot;DM&quot;_-;\-* #,##0.00\ &quot;DM&quot;_-;_-* &quot;-&quot;??\ &quot;DM&quot;_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0.00\ _D_M_-;\-* #,##0.00\ _D_M_-;_-* &quot;-&quot;??\ _D_M_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -33,16 +226,461 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="72"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF006100"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="MS Sans Serif"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -50,34 +688,394 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="62"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="18">
+  <cellStyleXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="174" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="173" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -126,25 +1124,229 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="18">
+  <cellStyles count="222">
+    <cellStyle name="20 % - Akzent1" xfId="35" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent2" xfId="38" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent3" xfId="41" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent4" xfId="44" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent5" xfId="47" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent6" xfId="50" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent1" xfId="36" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent2" xfId="39" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent3" xfId="42" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent4" xfId="45" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent5" xfId="48" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent6" xfId="51" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent1 2" xfId="150" xr:uid="{A561AF21-1B25-41C6-B83B-E0279F71E287}"/>
+    <cellStyle name="60 % - Akzent2 2" xfId="151" xr:uid="{AF206DBA-A73C-48B7-B6A5-53153DFBD462}"/>
+    <cellStyle name="60 % - Akzent3 2" xfId="152" xr:uid="{68DCD30B-0321-48E4-8AF9-D395CD312DFB}"/>
+    <cellStyle name="60 % - Akzent4 2" xfId="153" xr:uid="{18732857-444C-48F4-B281-ECAED06BF7FD}"/>
+    <cellStyle name="60 % - Akzent5 2" xfId="154" xr:uid="{4FA49055-48F4-47CE-AD26-E3DE5EFBEF52}"/>
+    <cellStyle name="60 % - Akzent6 2" xfId="155" xr:uid="{14544BAC-2944-43DD-8098-714911A5BD2D}"/>
+    <cellStyle name="Akzent1" xfId="34" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Akzent2" xfId="37" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Akzent3" xfId="40" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Akzent4" xfId="43" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Akzent5" xfId="46" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Akzent6" xfId="49" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Ausgabe" xfId="26" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Berechnung" xfId="27" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Comma 11" xfId="131" xr:uid="{341EAADA-8DA2-4C81-BDD2-E361FA772EAF}"/>
+    <cellStyle name="Comma 11 2" xfId="201" xr:uid="{8F1C90F4-27AF-42E7-8CF3-A3A94FFF9F85}"/>
+    <cellStyle name="Comma 2" xfId="55" xr:uid="{400F1DB3-DC87-48E1-A973-51378D66634C}"/>
+    <cellStyle name="Comma 2 10" xfId="182" xr:uid="{D6A4A637-AA32-47AA-9DA4-44E8EB399AF5}"/>
+    <cellStyle name="Comma 2 2" xfId="56" xr:uid="{F86EED8F-777B-4921-8BD8-2B718B1CF98E}"/>
+    <cellStyle name="Comma 2 2 2" xfId="183" xr:uid="{8A67292C-6E42-4831-8C23-55CACA027515}"/>
+    <cellStyle name="Comma 2 3" xfId="57" xr:uid="{A8499C8C-3B91-481B-B4F7-600DA3BD628C}"/>
+    <cellStyle name="Comma 2 3 2" xfId="58" xr:uid="{D7FE309F-EEAB-44BD-A68E-A441392F4F99}"/>
+    <cellStyle name="Comma 2 3 2 2" xfId="185" xr:uid="{4BE97BC1-5FD0-46AC-AE02-54CA063AB3DA}"/>
+    <cellStyle name="Comma 2 3 3" xfId="184" xr:uid="{709FEBF2-0EA7-4E6E-AF4B-20A26590B5B5}"/>
+    <cellStyle name="Comma 2 4" xfId="59" xr:uid="{02BEF201-3B55-42B3-B4AB-61B3DEAC0EDE}"/>
+    <cellStyle name="Comma 2 4 2" xfId="186" xr:uid="{88E0D09A-1775-49D6-95AA-9CDB8A275981}"/>
+    <cellStyle name="Comma 2 5" xfId="60" xr:uid="{F7CCD8DF-99CB-4163-88C0-CB277F26C5A9}"/>
+    <cellStyle name="Comma 2 5 2" xfId="187" xr:uid="{BD47C918-3071-448E-AF26-AB34E657703C}"/>
+    <cellStyle name="Comma 2 6" xfId="61" xr:uid="{AF563139-C222-427A-B178-5ED36A2431E3}"/>
+    <cellStyle name="Comma 2 6 2" xfId="188" xr:uid="{33A81FCF-C6B3-4E59-88DE-0B24A2A00ACF}"/>
+    <cellStyle name="Comma 2 7" xfId="62" xr:uid="{CB3423D9-B920-45EB-8CF1-B26A99ACC6A8}"/>
+    <cellStyle name="Comma 2 7 2" xfId="189" xr:uid="{1FF820E1-7630-411C-985F-54F20B40E639}"/>
+    <cellStyle name="Comma 2 8" xfId="63" xr:uid="{A645C93D-2A93-4EC0-B39B-B6194939B58B}"/>
+    <cellStyle name="Comma 2 8 2" xfId="190" xr:uid="{03D9B4BE-085C-4BE0-8225-7343D99B4AEF}"/>
+    <cellStyle name="Comma 2 9" xfId="64" xr:uid="{044DB7C7-1E8D-4ACF-8097-E5FDC12E58B2}"/>
+    <cellStyle name="Comma 2 9 2" xfId="191" xr:uid="{5B69667D-A940-470F-88B8-3524211773C6}"/>
+    <cellStyle name="Comma 3" xfId="65" xr:uid="{C8CECC75-FFF6-4801-B777-7A2CE11CDFB0}"/>
+    <cellStyle name="Comma 3 2" xfId="66" xr:uid="{FDE879B8-76E0-4434-832F-A452050DB684}"/>
+    <cellStyle name="Comma 3 2 2" xfId="193" xr:uid="{1270D171-B5FE-4D4A-A52B-4ABA31AB879B}"/>
+    <cellStyle name="Comma 3 3" xfId="192" xr:uid="{1E0B5357-AA4E-4A43-B176-CD4FA3602159}"/>
+    <cellStyle name="Comma 4" xfId="67" xr:uid="{42383F27-32D8-4C12-996C-9CEA738D5266}"/>
+    <cellStyle name="Comma 4 2" xfId="68" xr:uid="{3F1BDD3E-DDAC-45BE-8089-7B8E88D68CB7}"/>
+    <cellStyle name="Comma 4 2 2" xfId="172" xr:uid="{4C46288E-6FD1-4152-BD07-A7A69F70137E}"/>
+    <cellStyle name="Comma 4 2 2 2" xfId="217" xr:uid="{30D213E9-3F68-48C4-B788-69DCFAAA45AA}"/>
+    <cellStyle name="Comma 4 2 3" xfId="206" xr:uid="{6EFEA26B-5A3D-4AE9-AEC5-B34F730045BB}"/>
+    <cellStyle name="Comma 4 3" xfId="171" xr:uid="{CE0368F0-B754-4C06-9293-0FB4878EF231}"/>
+    <cellStyle name="Comma 4 3 2" xfId="216" xr:uid="{9B7D06BB-AD5D-444E-9025-7CA5C8DFCA1C}"/>
+    <cellStyle name="Comma 4 4" xfId="205" xr:uid="{F59CFD72-D592-41B6-BB49-49CF0E30029A}"/>
+    <cellStyle name="Comma 5" xfId="69" xr:uid="{1F93F990-AEC9-45D2-AC01-59BEDE8B02B0}"/>
+    <cellStyle name="Comma 5 2" xfId="70" xr:uid="{963ADEFC-6064-4159-9877-8F53A6BA92CB}"/>
+    <cellStyle name="Comma 5 2 2" xfId="195" xr:uid="{AB2377C4-7B23-4E06-8042-1F8DE94CD33F}"/>
+    <cellStyle name="Comma 5 3" xfId="194" xr:uid="{1CD603B4-A037-4EA3-9DEC-D7D4FCB46AA1}"/>
+    <cellStyle name="Comma 6" xfId="71" xr:uid="{7A96048E-C34A-48F0-97A5-724AD1F271A8}"/>
+    <cellStyle name="Comma 6 2" xfId="72" xr:uid="{79245297-BED7-45BE-A106-E362AC506235}"/>
+    <cellStyle name="Comma 6 2 2" xfId="197" xr:uid="{AE20E883-2B6D-48B7-9E3C-ED3BC0C3A5DA}"/>
+    <cellStyle name="Comma 6 3" xfId="73" xr:uid="{3F252B6F-C9CF-437D-83E4-5A1EAF3DC869}"/>
+    <cellStyle name="Comma 6 3 2" xfId="198" xr:uid="{06C5B3A3-5544-4544-ADB4-B4817ABA5612}"/>
+    <cellStyle name="Comma 6 4" xfId="196" xr:uid="{506C6270-3C92-4A37-B8B2-9AC29B18198E}"/>
+    <cellStyle name="Comma 7" xfId="74" xr:uid="{0A209EF4-0273-4BA5-AA47-CA67FF243486}"/>
+    <cellStyle name="Comma 7 2" xfId="199" xr:uid="{D83945D1-233C-4D4A-85A2-280DD05EDBA1}"/>
+    <cellStyle name="Comma 8" xfId="75" xr:uid="{9BB6C062-74ED-4EBF-9F24-DE17EC71508C}"/>
+    <cellStyle name="Comma 8 2" xfId="200" xr:uid="{F45B88D3-96E7-4CD3-B340-613D73B24720}"/>
+    <cellStyle name="Eingabe" xfId="25" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Ergebnis" xfId="33" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Erklärender Text" xfId="32" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good 2" xfId="76" xr:uid="{E4A52A2E-DCCB-437C-B836-F5911F2FC106}"/>
+    <cellStyle name="Gut" xfId="23" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1 2" xfId="77" xr:uid="{98D295B5-C1CE-44C8-9972-4B77856D2960}"/>
+    <cellStyle name="Heading 2 2" xfId="78" xr:uid="{49102A2A-1DB5-403F-ABA2-74666D95ADE5}"/>
+    <cellStyle name="Hyperlink 2" xfId="80" xr:uid="{9311D0EF-E87C-44E2-8E7B-25B733931E01}"/>
+    <cellStyle name="Hyperlink 2 2" xfId="138" xr:uid="{921DFD49-486E-45AB-B0BA-1F3F56A39CC6}"/>
+    <cellStyle name="Hyperlink 2 3" xfId="130" xr:uid="{90893881-3D81-411B-83A5-910A6DAE06D5}"/>
+    <cellStyle name="Hyperlink 2 3 2" xfId="132" xr:uid="{A52287F1-4316-4194-B60A-5698FF76C98C}"/>
+    <cellStyle name="Hyperlink 3" xfId="81" xr:uid="{682F7230-50B4-4AE6-8F24-B560A12329F9}"/>
     <cellStyle name="Komma 2" xfId="2" xr:uid="{AF1FA308-5BB0-4765-9052-001723E4E16E}"/>
     <cellStyle name="Komma 2 2" xfId="6" xr:uid="{546B1FA4-ED3D-4CCF-BFB1-6934F261636D}"/>
     <cellStyle name="Komma 2 2 2" xfId="7" xr:uid="{C0449768-2484-446A-AB6E-F20247C009BA}"/>
     <cellStyle name="Komma 2 2 2 2" xfId="9" xr:uid="{87EADEA1-1609-457D-98AF-3D679CF76F67}"/>
+    <cellStyle name="Komma 2 2 2 2 2" xfId="146" xr:uid="{868C18F1-C744-421E-A9F2-72A877EE1467}"/>
+    <cellStyle name="Komma 2 2 2 2 2 2" xfId="176" xr:uid="{16110CBB-6A72-4E38-B06C-EB982407B928}"/>
+    <cellStyle name="Komma 2 2 2 2 2 2 2" xfId="221" xr:uid="{B4EB86A8-4FBE-4723-955E-0F9BE14FA135}"/>
+    <cellStyle name="Komma 2 2 2 2 2 3" xfId="210" xr:uid="{D7E6CB5A-18A0-4C91-B2A3-BD3F03C4E84C}"/>
+    <cellStyle name="Komma 2 2 2 2 3" xfId="170" xr:uid="{A16B0968-2409-4B2C-9E75-4508C2AB1E9B}"/>
+    <cellStyle name="Komma 2 2 2 2 3 2" xfId="215" xr:uid="{932FB35D-4881-4C80-9F95-9BB093F61776}"/>
+    <cellStyle name="Komma 2 2 2 2 4" xfId="204" xr:uid="{1A094991-4803-4E41-B80E-328C65CCBC62}"/>
     <cellStyle name="Komma 2 2 2 3" xfId="11" xr:uid="{87EADEA1-1609-457D-98AF-3D679CF76F67}"/>
+    <cellStyle name="Komma 2 2 2 3 2" xfId="174" xr:uid="{AC9F418E-B252-4F8B-BBCB-175CB0294BCA}"/>
+    <cellStyle name="Komma 2 2 2 3 2 2" xfId="219" xr:uid="{2F55B75A-F868-4525-82D8-6188FD7734B6}"/>
+    <cellStyle name="Komma 2 2 2 3 3" xfId="208" xr:uid="{9687EBC5-A05E-4F1F-9C62-26B50E65C380}"/>
     <cellStyle name="Komma 2 2 2 4" xfId="13" xr:uid="{87EADEA1-1609-457D-98AF-3D679CF76F67}"/>
+    <cellStyle name="Komma 2 2 2 4 2" xfId="213" xr:uid="{AB858B1B-25B4-42F4-96CF-C291F13ED4C8}"/>
     <cellStyle name="Komma 2 2 2 5" xfId="15" xr:uid="{87EADEA1-1609-457D-98AF-3D679CF76F67}"/>
     <cellStyle name="Komma 2 2 2 6" xfId="17" xr:uid="{87EADEA1-1609-457D-98AF-3D679CF76F67}"/>
+    <cellStyle name="Komma 2 2 3" xfId="157" xr:uid="{EE84FF7F-362F-463D-8672-F789E9B89858}"/>
+    <cellStyle name="Komma 2 2 3 2" xfId="180" xr:uid="{0F8A9B17-2DF6-4350-85E3-0F3C02CC2E10}"/>
+    <cellStyle name="Komma 2 2 4" xfId="52" xr:uid="{CAEE5D63-6EA0-470C-B5E5-4ACB003CB7D1}"/>
     <cellStyle name="Komma 2 3" xfId="8" xr:uid="{D78E7949-E497-4216-AFE6-65271F7AA945}"/>
+    <cellStyle name="Komma 2 3 2" xfId="145" xr:uid="{B256EDE2-90FC-41AF-B58E-C0C45AB8BD14}"/>
+    <cellStyle name="Komma 2 3 2 2" xfId="175" xr:uid="{D5313480-F912-4434-8BD6-A15FC88E7FD1}"/>
+    <cellStyle name="Komma 2 3 2 2 2" xfId="220" xr:uid="{A5FE03C3-1E71-411B-A4B3-8FA19D8EF7D1}"/>
+    <cellStyle name="Komma 2 3 2 3" xfId="209" xr:uid="{847EA196-C477-4252-B841-C101141EC2E3}"/>
+    <cellStyle name="Komma 2 3 3" xfId="158" xr:uid="{22CDAA0E-9960-41BC-BDDC-29AA3ECFEDFC}"/>
+    <cellStyle name="Komma 2 3 4" xfId="169" xr:uid="{0F3515C4-F126-4845-BF15-9948DB81FAF9}"/>
+    <cellStyle name="Komma 2 3 4 2" xfId="214" xr:uid="{C9259D85-6E13-4449-9AB4-3EE3744EAC10}"/>
+    <cellStyle name="Komma 2 3 5" xfId="203" xr:uid="{A73DB940-81FD-423E-93F4-5CD1DCE6CD7C}"/>
     <cellStyle name="Komma 2 4" xfId="10" xr:uid="{D78E7949-E497-4216-AFE6-65271F7AA945}"/>
+    <cellStyle name="Komma 2 4 2" xfId="173" xr:uid="{11C6FD52-BF24-4B2F-8CE0-584C8FA39470}"/>
+    <cellStyle name="Komma 2 4 2 2" xfId="218" xr:uid="{FCC0B6C7-68CA-4FA2-831A-40298B8A6E1B}"/>
+    <cellStyle name="Komma 2 4 3" xfId="207" xr:uid="{0DC85B4A-7479-43C5-A6D2-07DCC271BE81}"/>
     <cellStyle name="Komma 2 5" xfId="12" xr:uid="{D78E7949-E497-4216-AFE6-65271F7AA945}"/>
+    <cellStyle name="Komma 2 5 2" xfId="148" xr:uid="{67D13653-98D5-4BD9-BABF-D06E4C5D2660}"/>
     <cellStyle name="Komma 2 6" xfId="14" xr:uid="{D78E7949-E497-4216-AFE6-65271F7AA945}"/>
+    <cellStyle name="Komma 2 6 2" xfId="212" xr:uid="{87AD2747-F1DE-4DBF-94CD-7B1D26818359}"/>
     <cellStyle name="Komma 2 7" xfId="16" xr:uid="{D78E7949-E497-4216-AFE6-65271F7AA945}"/>
+    <cellStyle name="Komma 3" xfId="54" xr:uid="{09D47CEA-8F0A-482D-9682-689214D2807A}"/>
+    <cellStyle name="Komma 3 2" xfId="156" xr:uid="{C49AC689-0450-46C8-BBD0-6144A4D415F9}"/>
+    <cellStyle name="Komma 3 2 2" xfId="181" xr:uid="{C6D818F1-2276-4A0C-95C3-AA8ADBB2C240}"/>
+    <cellStyle name="Komma 4" xfId="142" xr:uid="{9528749D-A4E1-4B4D-8973-123978130229}"/>
+    <cellStyle name="Komma 4 2" xfId="160" xr:uid="{02DF60B7-DB7A-4B53-8E49-9BF015B64825}"/>
+    <cellStyle name="Komma 4 2 2" xfId="202" xr:uid="{B18FF7AB-D510-4081-9814-D2C9CADAB3AD}"/>
+    <cellStyle name="Komma 4 2 3" xfId="211" xr:uid="{48E5D98D-FA60-4C98-A6A4-C71E0EAAEB26}"/>
+    <cellStyle name="Komma 5" xfId="162" xr:uid="{10FAD776-A812-40DC-BA7D-EC4DCB5244AB}"/>
+    <cellStyle name="Link 2" xfId="79" xr:uid="{8CB2C7F6-9C1F-4618-AB3E-ED672A39F44E}"/>
+    <cellStyle name="Link 2 2" xfId="163" xr:uid="{29DAFEE6-FAB3-4120-A47B-FBC24ADA3A85}"/>
+    <cellStyle name="Neutral 2" xfId="149" xr:uid="{A23AA3D9-DF94-4321-99A1-D5F457C5365E}"/>
+    <cellStyle name="Normal 10" xfId="82" xr:uid="{87E3B077-8E96-4AAF-B7D7-F6A89293BB2D}"/>
+    <cellStyle name="Normal 11" xfId="83" xr:uid="{40FB180A-1151-4000-B048-69F3E5C1DE3A}"/>
+    <cellStyle name="Normal 12" xfId="84" xr:uid="{7E8BBBAC-804F-4EEE-B5A9-F54893C2E48B}"/>
+    <cellStyle name="Normal 13" xfId="85" xr:uid="{BDA02F26-3E91-4887-B130-3CB211AC59AA}"/>
+    <cellStyle name="Normal 14" xfId="86" xr:uid="{275A191E-8B2A-4428-B5C9-E4F69AB8F161}"/>
+    <cellStyle name="Normal 15" xfId="87" xr:uid="{0373B41A-AF79-4D98-9849-F635AA691E17}"/>
+    <cellStyle name="Normal 16" xfId="88" xr:uid="{6B45D75E-0540-4F63-BB19-D4F0C7FF1C22}"/>
+    <cellStyle name="Normal 17" xfId="89" xr:uid="{58435A0C-1C4F-45CD-A68B-7E70879AFBD3}"/>
+    <cellStyle name="Normal 17 2" xfId="90" xr:uid="{261DFD6B-26F3-47C0-B1C4-CC0278C149DC}"/>
     <cellStyle name="Normal 2" xfId="4" xr:uid="{098744FE-9844-4518-A91E-00A8F4258A86}"/>
     <cellStyle name="Normal 2 2" xfId="5" xr:uid="{FCD300CD-8039-44DF-B12D-F1531F7C3F26}"/>
+    <cellStyle name="Normal 2 2 2" xfId="92" xr:uid="{845BE8A0-AF84-4349-808D-5F74E1C5F519}"/>
+    <cellStyle name="Normal 2 3" xfId="93" xr:uid="{26DAC670-3DBB-40C0-A178-17199513AD18}"/>
+    <cellStyle name="Normal 2 4" xfId="94" xr:uid="{099B2265-7963-43D4-93CC-A4CA52D10A10}"/>
+    <cellStyle name="Normal 2 5" xfId="91" xr:uid="{7A5E87BA-A0EB-4DE1-97EE-EB60399FD498}"/>
+    <cellStyle name="Normal 2 6" xfId="137" xr:uid="{54D0880C-9705-4D9B-B774-7B70372045F1}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{FA51F745-E432-4830-B289-30C69457E580}"/>
+    <cellStyle name="Normal 3 2" xfId="96" xr:uid="{87301416-CEBE-4CA1-9434-5C84BBEFC44F}"/>
+    <cellStyle name="Normal 3 2 2" xfId="97" xr:uid="{CCC79148-E4FC-4F12-8DC3-7A6DD3CCBFE4}"/>
+    <cellStyle name="Normal 3 3" xfId="98" xr:uid="{84E4F0A0-BB8A-467A-8E45-65F674D28B30}"/>
+    <cellStyle name="Normal 3 4" xfId="99" xr:uid="{761D3256-4DC6-4AB5-B05B-C1A713B19003}"/>
+    <cellStyle name="Normal 3 5" xfId="95" xr:uid="{D97A1B52-E8D7-4E28-ACCB-0FDD0CA9C1E6}"/>
+    <cellStyle name="Normal 4" xfId="100" xr:uid="{859DB6FE-D4F1-4E21-B3EE-A329687BCDA2}"/>
+    <cellStyle name="Normal 4 2" xfId="101" xr:uid="{D572C0DA-0347-4BC7-A734-4535BB5D6535}"/>
+    <cellStyle name="Normal 4 2 2" xfId="102" xr:uid="{6BF4D395-9620-4E07-8CA1-F3C87DF59135}"/>
+    <cellStyle name="Normal 4 3" xfId="103" xr:uid="{38ACCD26-7866-4992-93B5-65CB5D1218A6}"/>
+    <cellStyle name="Normal 4 3 2" xfId="135" xr:uid="{996E6719-0AE8-4F27-AB58-BEF6D351D6B6}"/>
+    <cellStyle name="Normal 4 4" xfId="104" xr:uid="{FB057024-2422-413F-AF3D-919DA7AF6949}"/>
+    <cellStyle name="Normal 4 5" xfId="136" xr:uid="{35D7D294-8172-45DA-957A-56678E2DF766}"/>
+    <cellStyle name="Normal 5" xfId="105" xr:uid="{FA5F6278-9CD6-44ED-AEFA-295B9D014A73}"/>
+    <cellStyle name="Normal 5 2" xfId="106" xr:uid="{F1B2D6EE-D6AB-499E-9235-A5BF544A56F2}"/>
+    <cellStyle name="Normal 6" xfId="107" xr:uid="{2CDD06CE-E9B5-4E57-AFEA-FCB9761AAD2A}"/>
+    <cellStyle name="Normal 6 2" xfId="108" xr:uid="{59102BA4-CF0D-411A-A4AC-8FBF4F74579A}"/>
+    <cellStyle name="Normal 7" xfId="109" xr:uid="{30BDE515-75E1-4E20-BE38-6E453E2D8ADE}"/>
+    <cellStyle name="Normal 7 2" xfId="110" xr:uid="{47A89D66-E8E3-418D-9C4E-19E5F64436C4}"/>
+    <cellStyle name="Normal 8" xfId="111" xr:uid="{ADB040F9-AFED-4CA4-B57A-54582F19A64E}"/>
+    <cellStyle name="Normal 8 2" xfId="112" xr:uid="{C6E028DB-B05E-4A32-A7F5-F72D67AB0BD6}"/>
+    <cellStyle name="Normal 8 3" xfId="113" xr:uid="{AD55282E-5F9E-457B-AD8F-BEB093706697}"/>
+    <cellStyle name="Normal 8 4" xfId="114" xr:uid="{EC49BECC-652F-4F95-89F0-D3E76D31C8E2}"/>
+    <cellStyle name="Normal 8 5" xfId="134" xr:uid="{5F75113F-2234-4403-902B-C71625177A9A}"/>
+    <cellStyle name="Normal 9" xfId="115" xr:uid="{86ECC189-174D-4AA6-B023-7AAF42FF64E4}"/>
+    <cellStyle name="Normal 9 2" xfId="116" xr:uid="{E0C3F1EB-C7EC-4847-A6BA-64825C8B8F71}"/>
+    <cellStyle name="Normal 9 3" xfId="117" xr:uid="{95EA2052-D4F2-45BD-8F84-BE7CFD15D76A}"/>
+    <cellStyle name="Notiz" xfId="31" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Notiz 2" xfId="168" xr:uid="{61B549CB-1D29-4286-95EB-64DC0617339C}"/>
+    <cellStyle name="Percent 2" xfId="119" xr:uid="{D4DD155A-9E3B-4922-9A1B-B521C4A7D7F3}"/>
+    <cellStyle name="Percent 3" xfId="120" xr:uid="{D0EC5F9B-F614-461E-96B3-0D77A9475A29}"/>
+    <cellStyle name="Percent 3 2" xfId="121" xr:uid="{E299C39E-C3D0-481A-9575-2EAF29D045EA}"/>
+    <cellStyle name="Percent 4" xfId="122" xr:uid="{89616573-1386-4DFB-962F-D14B2C0FF370}"/>
+    <cellStyle name="Percent 4 2" xfId="123" xr:uid="{D6E42022-3346-41D8-907E-84933609403E}"/>
+    <cellStyle name="Percent 5" xfId="124" xr:uid="{6DCFE8BD-D17B-4FB0-92D2-5C6AF4FDCA6F}"/>
+    <cellStyle name="Percent 5 2" xfId="125" xr:uid="{746B5A5A-B00F-42C4-83FA-B33F7BD1CF6B}"/>
+    <cellStyle name="Percent 6" xfId="126" xr:uid="{808D62D6-DF3C-40F4-9530-9FA368DF5966}"/>
+    <cellStyle name="Percent 6 2" xfId="127" xr:uid="{BD79AFED-D3E0-45E8-8532-2A49D29DEF8D}"/>
+    <cellStyle name="Percent 6 3" xfId="128" xr:uid="{5EC9DF2B-E127-4FB9-8C4D-25A1C5BEBFC7}"/>
+    <cellStyle name="Percent 7" xfId="129" xr:uid="{37B862EA-9687-4D5E-BBED-7459ECA41646}"/>
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Prozent 2" xfId="118" xr:uid="{D51F5D9B-8CA7-43E9-A3C1-F5F242C9F870}"/>
+    <cellStyle name="Prozent 3" xfId="133" xr:uid="{6FD1F7CB-7B8B-4AB5-9C0F-3EBD9640C461}"/>
+    <cellStyle name="Schlecht" xfId="24" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="53" xr:uid="{09688088-67F1-4CCD-BAB8-662F3344F479}"/>
+    <cellStyle name="Standard 2 2" xfId="167" xr:uid="{158ECFB9-CB4C-493F-8610-AF3E1277CC01}"/>
+    <cellStyle name="Standard 2 2 2" xfId="178" xr:uid="{D5C14800-72C9-4B34-BA80-12C25A2B2D4C}"/>
+    <cellStyle name="Standard 2 3" xfId="164" xr:uid="{A0C76BB9-01DE-42D5-AC25-4EFDD1B7304B}"/>
+    <cellStyle name="Standard 2 4" xfId="147" xr:uid="{908BD0CF-AB8B-4F82-A91D-503BC4324005}"/>
+    <cellStyle name="Standard 3" xfId="143" xr:uid="{F5876E7B-9EC4-404C-B82F-CC9646492953}"/>
+    <cellStyle name="Standard 3 2" xfId="166" xr:uid="{8A27AA64-B62A-4E73-83F6-14C208A4152F}"/>
+    <cellStyle name="Standard 3 2 2" xfId="179" xr:uid="{94F47BA1-1834-4E68-91D2-A0E9E4F676E6}"/>
+    <cellStyle name="Standard 4" xfId="144" xr:uid="{391B62B7-5AF5-4196-82E5-FD63B03CF618}"/>
+    <cellStyle name="Standard 4 2" xfId="161" xr:uid="{65765353-F5CC-4BEB-AFA6-371824CFEF7B}"/>
+    <cellStyle name="Standard 5" xfId="177" xr:uid="{E4979304-9B26-41FA-A0A9-C135B4499725}"/>
+    <cellStyle name="Überschrift" xfId="18" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1" xfId="19" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1 2" xfId="141" xr:uid="{3D20306D-48B9-408A-90A3-5EECEA66AE62}"/>
+    <cellStyle name="Überschrift 2" xfId="20" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Überschrift 2 2" xfId="140" xr:uid="{2C518ACA-FBFF-457C-AC75-0AC1A71428DC}"/>
+    <cellStyle name="Überschrift 3" xfId="21" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Überschrift 3 2" xfId="139" xr:uid="{552ED4A8-A314-4A8F-85B4-9598F5BDE921}"/>
+    <cellStyle name="Überschrift 4" xfId="22" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Überschrift 5" xfId="159" xr:uid="{3601D786-9073-4458-9749-B340096208E8}"/>
+    <cellStyle name="Verknüpfte Zelle" xfId="28" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Währung 2" xfId="165" xr:uid="{5628D56A-D9C2-4467-8A35-619D9F8547F1}"/>
+    <cellStyle name="Warnender Text" xfId="30" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Zelle überprüfen" xfId="29" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -474,6 +1676,1345 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A01CE75-70D6-4C19-A2E6-F011C88AB99E}">
+  <dimension ref="A4:W25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="12" max="12" width="7.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="48">
+        <v>4.25529007</v>
+      </c>
+      <c r="E5" s="48">
+        <v>2.6816</v>
+      </c>
+      <c r="F5" s="48">
+        <v>21.9</v>
+      </c>
+      <c r="G5" s="48">
+        <v>35.985833333333332</v>
+      </c>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="19"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <v>2030</v>
+      </c>
+      <c r="D6" s="49">
+        <v>3.2319999999999993</v>
+      </c>
+      <c r="E6" s="50">
+        <v>3.1009999999999991</v>
+      </c>
+      <c r="F6" s="51">
+        <v>26.302999999999884</v>
+      </c>
+      <c r="G6" s="52">
+        <v>32.632000000000062</v>
+      </c>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+    </row>
+    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <v>2035</v>
+      </c>
+      <c r="D7" s="49">
+        <v>3.7390000000000043</v>
+      </c>
+      <c r="E7" s="50">
+        <v>3.6844999999999857</v>
+      </c>
+      <c r="F7" s="51">
+        <v>31.403499999999894</v>
+      </c>
+      <c r="G7" s="52">
+        <v>37.153999999999996</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+    </row>
+    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>2040</v>
+      </c>
+      <c r="D8" s="49">
+        <v>4.2459999999999809</v>
+      </c>
+      <c r="E8" s="50">
+        <v>4.2679999999999723</v>
+      </c>
+      <c r="F8" s="51">
+        <v>36.503999999999905</v>
+      </c>
+      <c r="G8" s="52">
+        <v>41.675999999999931</v>
+      </c>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+    </row>
+    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>2045</v>
+      </c>
+      <c r="D9" s="49">
+        <v>4.7529999999999859</v>
+      </c>
+      <c r="E9" s="50">
+        <v>4.8514999999999873</v>
+      </c>
+      <c r="F9" s="51">
+        <v>41.604499999999916</v>
+      </c>
+      <c r="G9" s="52">
+        <v>46.198000000000093</v>
+      </c>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>2050</v>
+      </c>
+      <c r="D10" s="49">
+        <v>5.2599999999999909</v>
+      </c>
+      <c r="E10" s="50">
+        <v>5.4349999999999739</v>
+      </c>
+      <c r="F10" s="51">
+        <v>46.704999999999927</v>
+      </c>
+      <c r="G10" s="52">
+        <v>50.720000000000027</v>
+      </c>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+    </row>
+    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="20"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+    </row>
+    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+    </row>
+    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+    </row>
+    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FBAEC9-DD1D-41D4-AC07-D33C8D8DB1ED}">
+  <dimension ref="A4:I18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>2025</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="53">
+        <v>21.240000000000002</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>2030</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="53">
+        <v>21.240000000000002</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="20">
+        <v>2035</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="53">
+        <v>21.240000000000002</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="20">
+        <v>2040</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="53">
+        <v>21.240000000000002</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="20">
+        <v>2045</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="53">
+        <v>21.240000000000002</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="20">
+        <v>2050</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="53">
+        <v>21.240000000000002</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>2021</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="53">
+        <v>21.240000000000002</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>2022</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="53">
+        <v>21.240000000000002</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>2023</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" s="53">
+        <v>21.240000000000002</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14" s="13">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0</v>
+      </c>
+      <c r="F14" s="53">
+        <v>21.240000000000002</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18">
+        <v>0.23899999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF8A941-8ECB-48AC-B1FE-4E561D25CAD6}">
+  <dimension ref="A4:Q27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="5">
+        <v>60</v>
+      </c>
+      <c r="F5" s="5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>16.7</v>
+      </c>
+      <c r="H5">
+        <v>50</v>
+      </c>
+      <c r="M5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.439</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="E6" s="5">
+        <v>40</v>
+      </c>
+      <c r="F6" s="5">
+        <v>60</v>
+      </c>
+      <c r="G6">
+        <v>5.9</v>
+      </c>
+      <c r="H6">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="E7" s="5">
+        <v>40</v>
+      </c>
+      <c r="F7" s="5">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>5.9</v>
+      </c>
+      <c r="H7">
+        <v>49</v>
+      </c>
+      <c r="M7" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="E8" s="5">
+        <v>30</v>
+      </c>
+      <c r="F8" s="5">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>2.8</v>
+      </c>
+      <c r="H8">
+        <v>60</v>
+      </c>
+      <c r="M8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>30</v>
+      </c>
+      <c r="F9" s="5">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>0.1</v>
+      </c>
+      <c r="H9">
+        <v>24</v>
+      </c>
+      <c r="M9" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12">
+        <v>2025</v>
+      </c>
+      <c r="D12">
+        <v>2030</v>
+      </c>
+      <c r="E12" s="20">
+        <v>2035</v>
+      </c>
+      <c r="F12" s="20">
+        <v>2040</v>
+      </c>
+      <c r="G12" s="20">
+        <v>2045</v>
+      </c>
+      <c r="H12" s="20">
+        <v>2050</v>
+      </c>
+      <c r="I12">
+        <v>2021</v>
+      </c>
+      <c r="J12">
+        <v>2022</v>
+      </c>
+      <c r="K12">
+        <v>2023</v>
+      </c>
+      <c r="L12">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="29">
+        <v>9103.7199999999721</v>
+      </c>
+      <c r="D13" s="29">
+        <v>9103.7199999999721</v>
+      </c>
+      <c r="E13" s="29">
+        <v>9103.7199999999721</v>
+      </c>
+      <c r="F13" s="29">
+        <v>9103.7199999999721</v>
+      </c>
+      <c r="G13" s="29">
+        <v>9103.7199999999721</v>
+      </c>
+      <c r="H13" s="29">
+        <v>9103.7199999999721</v>
+      </c>
+      <c r="I13" s="29">
+        <v>9103.7199999999721</v>
+      </c>
+      <c r="J13" s="29">
+        <v>9103.7199999999721</v>
+      </c>
+      <c r="K13" s="29">
+        <v>9103.7199999999721</v>
+      </c>
+      <c r="L13" s="29">
+        <v>9103.7199999999721</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="31">
+        <v>3199.1199999999953</v>
+      </c>
+      <c r="D14" s="38">
+        <v>3199.1199999999953</v>
+      </c>
+      <c r="E14" s="38">
+        <v>3199.1199999999953</v>
+      </c>
+      <c r="F14" s="38">
+        <v>3199.1199999999953</v>
+      </c>
+      <c r="G14" s="38">
+        <v>3199.1199999999953</v>
+      </c>
+      <c r="H14" s="38">
+        <v>3199.1199999999953</v>
+      </c>
+      <c r="I14" s="38">
+        <v>3199.1199999999953</v>
+      </c>
+      <c r="J14" s="38">
+        <v>3199.1199999999953</v>
+      </c>
+      <c r="K14" s="38">
+        <v>3199.1199999999953</v>
+      </c>
+      <c r="L14" s="38">
+        <v>3199.1199999999953</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="33">
+        <v>3828.4799999999814</v>
+      </c>
+      <c r="D15" s="38">
+        <v>3828.4799999999814</v>
+      </c>
+      <c r="E15" s="38">
+        <v>3828.4799999999814</v>
+      </c>
+      <c r="F15" s="38">
+        <v>3828.4799999999814</v>
+      </c>
+      <c r="G15" s="38">
+        <v>3828.4799999999814</v>
+      </c>
+      <c r="H15" s="38">
+        <v>3828.4799999999814</v>
+      </c>
+      <c r="I15" s="38">
+        <v>3828.4799999999814</v>
+      </c>
+      <c r="J15" s="38">
+        <v>3828.4799999999814</v>
+      </c>
+      <c r="K15" s="38">
+        <v>3828.4799999999814</v>
+      </c>
+      <c r="L15" s="38">
+        <v>3828.4799999999814</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="35">
+        <v>970.94640000000072</v>
+      </c>
+      <c r="D16" s="38">
+        <v>970.94640000000072</v>
+      </c>
+      <c r="E16" s="38">
+        <v>970.94640000000072</v>
+      </c>
+      <c r="F16" s="38">
+        <v>970.94640000000072</v>
+      </c>
+      <c r="G16" s="38">
+        <v>970.94640000000072</v>
+      </c>
+      <c r="H16" s="38">
+        <v>970.94640000000072</v>
+      </c>
+      <c r="I16" s="38">
+        <v>970.94640000000072</v>
+      </c>
+      <c r="J16" s="38">
+        <v>970.94640000000072</v>
+      </c>
+      <c r="K16" s="38">
+        <v>970.94640000000072</v>
+      </c>
+      <c r="L16" s="38">
+        <v>970.94640000000072</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="37">
+        <v>801.85599999999977</v>
+      </c>
+      <c r="D17" s="38">
+        <v>801.85599999999977</v>
+      </c>
+      <c r="E17" s="38">
+        <v>801.85599999999977</v>
+      </c>
+      <c r="F17" s="38">
+        <v>801.85599999999977</v>
+      </c>
+      <c r="G17" s="38">
+        <v>801.85599999999977</v>
+      </c>
+      <c r="H17" s="38">
+        <v>801.85599999999977</v>
+      </c>
+      <c r="I17" s="38">
+        <v>801.85599999999977</v>
+      </c>
+      <c r="J17" s="38">
+        <v>801.85599999999977</v>
+      </c>
+      <c r="K17" s="38">
+        <v>801.85599999999977</v>
+      </c>
+      <c r="L17" s="38">
+        <v>801.85599999999977</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="20">
+        <v>2025</v>
+      </c>
+      <c r="D19" s="20">
+        <v>2030</v>
+      </c>
+      <c r="E19" s="20">
+        <v>2035</v>
+      </c>
+      <c r="F19" s="20">
+        <v>2040</v>
+      </c>
+      <c r="G19" s="20">
+        <v>2045</v>
+      </c>
+      <c r="H19" s="20">
+        <v>2050</v>
+      </c>
+      <c r="I19">
+        <v>2021</v>
+      </c>
+      <c r="J19">
+        <v>2022</v>
+      </c>
+      <c r="K19">
+        <v>2023</v>
+      </c>
+      <c r="L19">
+        <v>2024</v>
+      </c>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="30">
+        <v>126.41439999999966</v>
+      </c>
+      <c r="D20" s="30">
+        <v>126.41439999999966</v>
+      </c>
+      <c r="E20" s="30">
+        <v>126.41439999999966</v>
+      </c>
+      <c r="F20" s="30">
+        <v>126.41439999999966</v>
+      </c>
+      <c r="G20" s="30">
+        <v>126.41439999999966</v>
+      </c>
+      <c r="H20" s="30">
+        <v>126.41439999999966</v>
+      </c>
+      <c r="I20" s="30">
+        <v>126.41439999999966</v>
+      </c>
+      <c r="J20" s="30">
+        <v>126.41439999999966</v>
+      </c>
+      <c r="K20" s="30">
+        <v>126.41439999999966</v>
+      </c>
+      <c r="L20" s="30">
+        <v>126.41439999999966</v>
+      </c>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="32">
+        <v>59.900000000000546</v>
+      </c>
+      <c r="D21" s="38">
+        <v>59.900000000000546</v>
+      </c>
+      <c r="E21" s="38">
+        <v>59.900000000000546</v>
+      </c>
+      <c r="F21" s="38">
+        <v>59.900000000000546</v>
+      </c>
+      <c r="G21" s="38">
+        <v>59.900000000000546</v>
+      </c>
+      <c r="H21" s="38">
+        <v>59.900000000000546</v>
+      </c>
+      <c r="I21" s="38">
+        <v>59.900000000000546</v>
+      </c>
+      <c r="J21" s="38">
+        <v>59.900000000000546</v>
+      </c>
+      <c r="K21" s="38">
+        <v>59.900000000000546</v>
+      </c>
+      <c r="L21" s="38">
+        <v>59.900000000000546</v>
+      </c>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="34">
+        <v>58.740000000000236</v>
+      </c>
+      <c r="D22" s="38">
+        <v>58.740000000000236</v>
+      </c>
+      <c r="E22" s="38">
+        <v>58.740000000000236</v>
+      </c>
+      <c r="F22" s="38">
+        <v>58.740000000000236</v>
+      </c>
+      <c r="G22" s="38">
+        <v>58.740000000000236</v>
+      </c>
+      <c r="H22" s="38">
+        <v>58.740000000000236</v>
+      </c>
+      <c r="I22" s="38">
+        <v>58.740000000000236</v>
+      </c>
+      <c r="J22" s="38">
+        <v>58.740000000000236</v>
+      </c>
+      <c r="K22" s="38">
+        <v>58.740000000000236</v>
+      </c>
+      <c r="L22" s="38">
+        <v>58.740000000000236</v>
+      </c>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="36">
+        <v>21.099199999999882</v>
+      </c>
+      <c r="D23" s="38">
+        <v>21.099199999999882</v>
+      </c>
+      <c r="E23" s="38">
+        <v>21.099199999999882</v>
+      </c>
+      <c r="F23" s="38">
+        <v>21.099199999999882</v>
+      </c>
+      <c r="G23" s="38">
+        <v>21.099199999999882</v>
+      </c>
+      <c r="H23" s="38">
+        <v>21.099199999999882</v>
+      </c>
+      <c r="I23" s="38">
+        <v>21.099199999999882</v>
+      </c>
+      <c r="J23" s="38">
+        <v>21.099199999999882</v>
+      </c>
+      <c r="K23" s="38">
+        <v>21.099199999999882</v>
+      </c>
+      <c r="L23" s="38">
+        <v>21.099199999999882</v>
+      </c>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="38">
+        <v>12.23599999999999</v>
+      </c>
+      <c r="D24" s="38">
+        <v>12.23599999999999</v>
+      </c>
+      <c r="E24" s="38">
+        <v>12.23599999999999</v>
+      </c>
+      <c r="F24" s="38">
+        <v>12.23599999999999</v>
+      </c>
+      <c r="G24" s="38">
+        <v>12.23599999999999</v>
+      </c>
+      <c r="H24" s="38">
+        <v>12.23599999999999</v>
+      </c>
+      <c r="I24" s="38">
+        <v>12.23599999999999</v>
+      </c>
+      <c r="J24" s="38">
+        <v>12.23599999999999</v>
+      </c>
+      <c r="K24" s="38">
+        <v>12.23599999999999</v>
+      </c>
+      <c r="L24" s="38">
+        <v>12.23599999999999</v>
+      </c>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P25" s="14"/>
+      <c r="Q25" s="14"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCCED0B7-B92C-4306-AF7A-9D3ACEBB12F2}">
+  <dimension ref="C5:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5776775-C2C6-4090-A4FF-E8AB4F9F35A2}">
   <dimension ref="A4:R57"/>
